--- a/Result/profitability/2408.xlsx
+++ b/Result/profitability/2408.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.88</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9587500000000001</v>
+        <v>2.85125</v>
       </c>
       <c r="N2" t="n">
-        <v>4.73125</v>
+        <v>14.2625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.56</v>
       </c>
       <c r="M3" t="n">
-        <v>0.82375</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5450000000000008</v>
+        <v>11.80125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.88</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6525000000000001</v>
+        <v>2.56375</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.5725</v>
+        <v>9.232499999999998</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.54</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4137500000000001</v>
+        <v>2.41125</v>
       </c>
       <c r="N5" t="n">
-        <v>-12.39375</v>
+        <v>0.1125000000000007</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2975000000000001</v>
+        <v>2.0675</v>
       </c>
       <c r="N6" t="n">
-        <v>-24.05625</v>
+        <v>-16.42625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-3.09</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1512499999999998</v>
+        <v>1.23375</v>
       </c>
       <c r="N7" t="n">
-        <v>-32.14</v>
+        <v>-28.335</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-1.72</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8137499999999999</v>
+        <v>-0.03249999999999995</v>
       </c>
       <c r="N8" t="n">
-        <v>-39.55</v>
+        <v>-38.1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>82549</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16932</v>
+      </c>
+      <c r="E75" t="n">
+        <v>65617</v>
+      </c>
+      <c r="F75" t="n">
+        <v>79.48999999999999</v>
+      </c>
+      <c r="G75" t="n">
+        <v>60826</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>73.68%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1503</v>
+      </c>
+      <c r="J75" t="n">
+        <v>62329</v>
+      </c>
+      <c r="K75" t="n">
+        <v>50192</v>
+      </c>
+      <c r="L75" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.02625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.50625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7431629013079666</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>11.59999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1708646339667108</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-12.10606060606061</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-4.86624513618677</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
